--- a/output/graficos_dimensiones/comunal_e_matricula_a_2023_o_higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2023_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:26</t>
+    <t xml:space="preserve">2026-09-10 01:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2023_o_higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2023_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:41</t>
+    <t xml:space="preserve">2026-09-18 11:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2023_o_higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2023_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:37</t>
+    <t xml:space="preserve">2026-09-23 15:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2023_o_higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2023_o_higgins.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Litueche</t>
   </si>
   <si>
-    <t xml:space="preserve">Marchihue</t>
+    <t xml:space="preserve">Marchigüe</t>
   </si>
   <si>
     <t xml:space="preserve">Navidad</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 15:43</t>
+    <t xml:space="preserve">2026-10-04 10:49</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2023_o_higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2023_o_higgins.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:49</t>
+    <t xml:space="preserve">2026-10-05 16:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -982,7 +982,7 @@
         <v>97.58</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>103.12</v>
+        <v>103.13</v>
       </c>
       <c r="I15" s="2" t="n">
         <v>60.32</v>
@@ -1295,7 +1295,7 @@
         <v>42.45</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>65.62</v>
+        <v>65.63</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>100.12</v>
